--- a/assignment3/data/trainingdataset_ontario_budgets_v15_llm_sample.xlsx
+++ b/assignment3/data/trainingdataset_ontario_budgets_v15_llm_sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramurphy/Documents/GitHub/text-analysis-public-university-llm/assignment3/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9012BF38-4063-794B-AE8A-5E4AE50A96FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32ADCBB0-093F-B047-AC90-51D363BF21BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6620" yWindow="540" windowWidth="30160" windowHeight="19660" xr2:uid="{FB597964-1960-7349-B80F-395C3D8D9DDC}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="414">
   <si>
     <t>document</t>
   </si>
@@ -135,9 +135,6 @@
     <t>The Ministry has not yet announced what the tuition framework will be over the second and third year of this budget planning time frame. However, the budget continues to assume the same tuition framework will continue which limits tuition fee growth to an institutional average of 3%. Unviersities continue to await an announcement on the future of the new tuition framework. </t>
   </si>
   <si>
-    <t>Previously, all institutions were requested to move to approving tuition fees two years ahead to facilitate the implementation of net-tuition billing. As a result, we had intended on bringing fees for 2019-20 to March board. However, due to the delay in the announcement of the next tuition framework we have post-poned the approval of the fees for 2019-20 until the Ministry announces what the new tuition framework will be for 2019-20. </t>
-  </si>
-  <si>
     <t>The University’s strategic framework promotes the vision of Queen’s University as the Canadian research-intensive university with a transformative student learning experience. The guiding policies of the framework address the two key features of the quintessential balanced academy, the student learning experience and research prominence, while paying appropriate attention at the same time to the need for increased internationalization and financial sustainability. The framework will guide academic, and thus financial, priorities. </t>
   </si>
   <si>
@@ -148,9 +145,6 @@
   </si>
   <si>
     <t>queens_2018_7</t>
-  </si>
-  <si>
-    <t>queens_2018_8</t>
   </si>
   <si>
     <t>queens_2018_9</t>
@@ -2723,7 +2717,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U186"/>
+  <dimension ref="A1:U185"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -2750,19 +2744,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>5</v>
@@ -2786,22 +2780,22 @@
         <v>15</v>
       </c>
       <c r="P1" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="R1" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="R1" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="T1" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="28" customHeight="1">
@@ -2818,7 +2812,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F2" s="13">
         <v>1</v>
@@ -2865,7 +2859,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F3" s="13">
         <v>1</v>
@@ -2912,7 +2906,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F4" s="13">
         <v>1</v>
@@ -2959,13 +2953,13 @@
         <v>1</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F5" s="13">
         <v>1</v>
       </c>
       <c r="G5" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" s="13">
         <v>1</v>
@@ -3006,7 +3000,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F6" s="13">
         <v>1</v>
@@ -3056,7 +3050,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" s="13">
         <v>1</v>
@@ -3097,7 +3091,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F8" s="13">
         <v>1</v>
@@ -3135,7 +3129,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>29</v>
@@ -3144,7 +3138,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F9" s="13">
         <v>1</v>
@@ -3182,7 +3176,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>30</v>
@@ -3191,13 +3185,13 @@
         <v>1</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F10" s="13">
         <v>1</v>
       </c>
       <c r="G10" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" s="13">
         <v>1</v>
@@ -3229,7 +3223,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>31</v>
@@ -3238,7 +3232,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F11" s="13">
         <v>1</v>
@@ -3276,28 +3270,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D12" s="13">
-        <v>1</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>399</v>
+        <v>0</v>
       </c>
       <c r="F12" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="13">
         <v>0</v>
       </c>
       <c r="H12" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J12" s="4">
         <v>9</v>
@@ -3320,31 +3311,34 @@
     </row>
     <row r="13" spans="1:21">
       <c r="A13" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="D13" s="13">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>395</v>
       </c>
       <c r="F13" s="13">
         <v>1</v>
       </c>
       <c r="G13" s="13">
+        <v>1</v>
+      </c>
+      <c r="H13" s="13">
         <v>2</v>
       </c>
-      <c r="H13" s="13">
-        <v>1</v>
-      </c>
       <c r="I13" s="4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J13" s="4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>11</v>
@@ -3353,13 +3347,13 @@
         <v>13</v>
       </c>
       <c r="M13" s="4">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="N13" s="4">
         <v>1</v>
       </c>
       <c r="O13" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -3367,16 +3361,16 @@
         <v>7</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" s="13">
         <v>1</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F14" s="13">
         <v>1</v>
@@ -3388,7 +3382,7 @@
         <v>2</v>
       </c>
       <c r="I14" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="4">
         <v>7</v>
@@ -3414,28 +3408,28 @@
         <v>7</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="D15" s="13">
         <v>1</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F15" s="13">
         <v>1</v>
       </c>
       <c r="G15" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J15" s="4">
         <v>7</v>
@@ -3461,28 +3455,28 @@
         <v>7</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" s="13">
         <v>1</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F16" s="13">
         <v>1</v>
       </c>
       <c r="G16" s="13">
+        <v>1</v>
+      </c>
+      <c r="H16" s="13">
         <v>2</v>
       </c>
-      <c r="H16" s="13">
-        <v>1</v>
-      </c>
       <c r="I16" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J16" s="4">
         <v>7</v>
@@ -3508,28 +3502,25 @@
         <v>7</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D17" s="13">
-        <v>1</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>401</v>
+        <v>0</v>
       </c>
       <c r="F17" s="13">
         <v>1</v>
       </c>
       <c r="G17" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J17" s="4">
         <v>7</v>
@@ -3552,31 +3543,34 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="4" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D18" s="13">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>395</v>
       </c>
       <c r="F18" s="13">
         <v>1</v>
       </c>
       <c r="G18" s="13">
+        <v>1</v>
+      </c>
+      <c r="H18" s="13">
         <v>2</v>
       </c>
-      <c r="H18" s="13">
-        <v>1</v>
-      </c>
       <c r="I18" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J18" s="4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>11</v>
@@ -3585,7 +3579,7 @@
         <v>13</v>
       </c>
       <c r="M18" s="4">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="N18" s="4">
         <v>1</v>
@@ -3596,19 +3590,19 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" s="13">
         <v>1</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F19" s="13">
         <v>1</v>
@@ -3620,7 +3614,7 @@
         <v>2</v>
       </c>
       <c r="I19" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J19" s="4">
         <v>10</v>
@@ -3643,19 +3637,19 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>51</v>
+        <v>269</v>
       </c>
       <c r="D20" s="13">
         <v>1</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="F20" s="13">
         <v>1</v>
@@ -3667,7 +3661,7 @@
         <v>2</v>
       </c>
       <c r="I20" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J20" s="4">
         <v>10</v>
@@ -3690,31 +3684,31 @@
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>271</v>
+        <v>50</v>
       </c>
       <c r="D21" s="13">
         <v>1</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F21" s="13">
         <v>1</v>
       </c>
       <c r="G21" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J21" s="4">
         <v>10</v>
@@ -3737,31 +3731,31 @@
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>57</v>
+        <v>268</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D22" s="13">
         <v>1</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F22" s="13">
         <v>1</v>
       </c>
       <c r="G22" s="13">
+        <v>1</v>
+      </c>
+      <c r="H22" s="13">
         <v>2</v>
       </c>
-      <c r="H22" s="13">
-        <v>1</v>
-      </c>
       <c r="I22" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22" s="4">
         <v>10</v>
@@ -3784,19 +3778,19 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="4" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>270</v>
+        <v>57</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D23" s="13">
         <v>1</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="F23" s="13">
         <v>1</v>
@@ -3808,10 +3802,10 @@
         <v>2</v>
       </c>
       <c r="I23" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J23" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>11</v>
@@ -3820,7 +3814,7 @@
         <v>13</v>
       </c>
       <c r="M23" s="4">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="N23" s="4">
         <v>1</v>
@@ -3831,19 +3825,19 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D24" s="13">
         <v>1</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F24" s="13">
         <v>1</v>
@@ -3855,7 +3849,7 @@
         <v>2</v>
       </c>
       <c r="I24" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24" s="4">
         <v>6</v>
@@ -3878,19 +3872,19 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>51</v>
+        <v>62</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>59</v>
       </c>
       <c r="D25" s="13">
         <v>1</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="F25" s="13">
         <v>1</v>
@@ -3902,7 +3896,7 @@
         <v>2</v>
       </c>
       <c r="I25" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J25" s="4">
         <v>6</v>
@@ -3925,31 +3919,31 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D26" s="13">
         <v>1</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F26" s="13">
         <v>1</v>
       </c>
       <c r="G26" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26" s="4">
         <v>6</v>
@@ -3972,34 +3966,34 @@
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="4" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>65</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D27" s="13">
         <v>1</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="F27" s="13">
         <v>1</v>
       </c>
       <c r="G27" s="13">
+        <v>1</v>
+      </c>
+      <c r="H27" s="13">
         <v>2</v>
       </c>
-      <c r="H27" s="13">
-        <v>1</v>
-      </c>
       <c r="I27" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J27" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>11</v>
@@ -4008,7 +4002,7 @@
         <v>13</v>
       </c>
       <c r="M27" s="4">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="N27" s="4">
         <v>1</v>
@@ -4019,19 +4013,19 @@
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D28" s="13">
         <v>1</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F28" s="13">
         <v>1</v>
@@ -4043,7 +4037,7 @@
         <v>2</v>
       </c>
       <c r="I28" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" s="4">
         <v>7</v>
@@ -4066,19 +4060,19 @@
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>51</v>
-      </c>
       <c r="D29" s="13">
         <v>1</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F29" s="13">
         <v>1</v>
@@ -4090,7 +4084,7 @@
         <v>2</v>
       </c>
       <c r="I29" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="4">
         <v>7</v>
@@ -4113,19 +4107,19 @@
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D30" s="13">
         <v>1</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F30" s="13">
         <v>1</v>
@@ -4137,7 +4131,7 @@
         <v>2</v>
       </c>
       <c r="I30" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="4">
         <v>7</v>
@@ -4160,19 +4154,19 @@
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D31" s="13">
         <v>1</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F31" s="13">
         <v>1</v>
@@ -4184,7 +4178,7 @@
         <v>2</v>
       </c>
       <c r="I31" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J31" s="4">
         <v>7</v>
@@ -4207,13 +4201,13 @@
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D32" s="13">
         <v>1</v>
@@ -4225,13 +4219,13 @@
         <v>1</v>
       </c>
       <c r="G32" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J32" s="4">
         <v>7</v>
@@ -4254,31 +4248,31 @@
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D33" s="13">
         <v>1</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F33" s="13">
         <v>1</v>
       </c>
       <c r="G33" s="13">
+        <v>1</v>
+      </c>
+      <c r="H33" s="13">
         <v>2</v>
       </c>
-      <c r="H33" s="13">
-        <v>1</v>
-      </c>
       <c r="I33" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J33" s="4">
         <v>7</v>
@@ -4301,19 +4295,19 @@
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="4" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D34" s="13">
         <v>1</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="F34" s="13">
         <v>1</v>
@@ -4325,10 +4319,10 @@
         <v>2</v>
       </c>
       <c r="I34" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J34" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>11</v>
@@ -4337,7 +4331,7 @@
         <v>13</v>
       </c>
       <c r="M34" s="4">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="N34" s="4">
         <v>1</v>
@@ -4348,19 +4342,19 @@
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>81</v>
-      </c>
       <c r="D35" s="13">
         <v>1</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F35" s="13">
         <v>1</v>
@@ -4372,7 +4366,7 @@
         <v>2</v>
       </c>
       <c r="I35" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" s="4">
         <v>8</v>
@@ -4395,19 +4389,19 @@
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D36" s="13">
         <v>1</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F36" s="13">
         <v>1</v>
@@ -4419,7 +4413,7 @@
         <v>2</v>
       </c>
       <c r="I36" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J36" s="4">
         <v>8</v>
@@ -4442,19 +4436,19 @@
     </row>
     <row r="37" spans="1:15">
       <c r="A37" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D37" s="13">
         <v>1</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F37" s="13">
         <v>1</v>
@@ -4466,7 +4460,7 @@
         <v>2</v>
       </c>
       <c r="I37" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J37" s="4">
         <v>8</v>
@@ -4489,19 +4483,19 @@
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D38" s="13">
         <v>1</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F38" s="13">
         <v>1</v>
@@ -4513,7 +4507,7 @@
         <v>2</v>
       </c>
       <c r="I38" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J38" s="4">
         <v>8</v>
@@ -4536,31 +4530,31 @@
     </row>
     <row r="39" spans="1:15">
       <c r="A39" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D39" s="13">
         <v>1</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F39" s="13">
         <v>1</v>
       </c>
       <c r="G39" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I39" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J39" s="4">
         <v>8</v>
@@ -4583,31 +4577,31 @@
     </row>
     <row r="40" spans="1:15">
       <c r="A40" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D40" s="13">
         <v>1</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F40" s="13">
         <v>1</v>
       </c>
       <c r="G40" s="13">
+        <v>1</v>
+      </c>
+      <c r="H40" s="13">
         <v>2</v>
       </c>
-      <c r="H40" s="13">
-        <v>1</v>
-      </c>
       <c r="I40" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J40" s="4">
         <v>8</v>
@@ -4630,19 +4624,19 @@
     </row>
     <row r="41" spans="1:15">
       <c r="A41" s="4" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>93</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D41" s="13">
         <v>1</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="F41" s="13">
         <v>1</v>
@@ -4654,7 +4648,7 @@
         <v>2</v>
       </c>
       <c r="I41" s="4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J41" s="4">
         <v>8</v>
@@ -4666,7 +4660,7 @@
         <v>13</v>
       </c>
       <c r="M41" s="4">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="N41" s="4">
         <v>1</v>
@@ -4677,19 +4671,19 @@
     </row>
     <row r="42" spans="1:15">
       <c r="A42" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C42" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C42" s="9" t="s">
-        <v>96</v>
-      </c>
       <c r="D42" s="13">
         <v>1</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F42" s="13">
         <v>1</v>
@@ -4701,7 +4695,7 @@
         <v>2</v>
       </c>
       <c r="I42" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" s="4">
         <v>8</v>
@@ -4724,19 +4718,19 @@
     </row>
     <row r="43" spans="1:15">
       <c r="A43" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D43" s="13">
         <v>1</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F43" s="13">
         <v>1</v>
@@ -4748,7 +4742,7 @@
         <v>2</v>
       </c>
       <c r="I43" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J43" s="4">
         <v>8</v>
@@ -4771,19 +4765,19 @@
     </row>
     <row r="44" spans="1:15">
       <c r="A44" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="D44" s="13">
         <v>1</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F44" s="13">
         <v>1</v>
@@ -4795,7 +4789,7 @@
         <v>2</v>
       </c>
       <c r="I44" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J44" s="4">
         <v>8</v>
@@ -4818,19 +4812,19 @@
     </row>
     <row r="45" spans="1:15">
       <c r="A45" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D45" s="13">
         <v>1</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F45" s="13">
         <v>1</v>
@@ -4842,7 +4836,7 @@
         <v>2</v>
       </c>
       <c r="I45" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J45" s="4">
         <v>8</v>
@@ -4865,13 +4859,13 @@
     </row>
     <row r="46" spans="1:15">
       <c r="A46" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D46" s="13">
         <v>1</v>
@@ -4883,13 +4877,13 @@
         <v>1</v>
       </c>
       <c r="G46" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J46" s="4">
         <v>8</v>
@@ -4912,31 +4906,31 @@
     </row>
     <row r="47" spans="1:15">
       <c r="A47" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D47" s="13">
         <v>1</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F47" s="13">
         <v>1</v>
       </c>
       <c r="G47" s="13">
+        <v>1</v>
+      </c>
+      <c r="H47" s="13">
         <v>2</v>
       </c>
-      <c r="H47" s="13">
-        <v>1</v>
-      </c>
       <c r="I47" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J47" s="4">
         <v>8</v>
@@ -4959,19 +4953,19 @@
     </row>
     <row r="48" spans="1:15">
       <c r="A48" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D48" s="13">
         <v>1</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F48" s="13">
         <v>1</v>
@@ -4983,7 +4977,7 @@
         <v>2</v>
       </c>
       <c r="I48" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J48" s="4">
         <v>8</v>
@@ -5006,19 +5000,19 @@
     </row>
     <row r="49" spans="1:15">
       <c r="A49" s="4" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>109</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D49" s="13">
         <v>1</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="F49" s="13">
         <v>1</v>
@@ -5030,7 +5024,7 @@
         <v>2</v>
       </c>
       <c r="I49" s="4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J49" s="4">
         <v>8</v>
@@ -5042,7 +5036,7 @@
         <v>13</v>
       </c>
       <c r="M49" s="4">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="N49" s="4">
         <v>1</v>
@@ -5053,19 +5047,19 @@
     </row>
     <row r="50" spans="1:15">
       <c r="A50" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B50" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="C50" s="9" t="s">
-        <v>112</v>
-      </c>
       <c r="D50" s="13">
         <v>1</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F50" s="13">
         <v>1</v>
@@ -5077,7 +5071,7 @@
         <v>2</v>
       </c>
       <c r="I50" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J50" s="4">
         <v>8</v>
@@ -5100,19 +5094,19 @@
     </row>
     <row r="51" spans="1:15">
       <c r="A51" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D51" s="13">
         <v>1</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F51" s="13">
         <v>1</v>
@@ -5124,7 +5118,7 @@
         <v>2</v>
       </c>
       <c r="I51" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J51" s="4">
         <v>8</v>
@@ -5147,19 +5141,19 @@
     </row>
     <row r="52" spans="1:15">
       <c r="A52" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D52" s="13">
         <v>1</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F52" s="13">
         <v>1</v>
@@ -5171,7 +5165,7 @@
         <v>2</v>
       </c>
       <c r="I52" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J52" s="4">
         <v>8</v>
@@ -5194,13 +5188,13 @@
     </row>
     <row r="53" spans="1:15">
       <c r="A53" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D53" s="13">
         <v>1</v>
@@ -5212,13 +5206,13 @@
         <v>1</v>
       </c>
       <c r="G53" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J53" s="4">
         <v>8</v>
@@ -5241,31 +5235,31 @@
     </row>
     <row r="54" spans="1:15">
       <c r="A54" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D54" s="13">
         <v>1</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F54" s="13">
         <v>1</v>
       </c>
       <c r="G54" s="13">
+        <v>1</v>
+      </c>
+      <c r="H54" s="13">
         <v>2</v>
       </c>
-      <c r="H54" s="13">
-        <v>1</v>
-      </c>
       <c r="I54" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J54" s="4">
         <v>8</v>
@@ -5288,19 +5282,19 @@
     </row>
     <row r="55" spans="1:15">
       <c r="A55" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D55" s="13">
         <v>1</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F55" s="13">
         <v>1</v>
@@ -5312,7 +5306,7 @@
         <v>2</v>
       </c>
       <c r="I55" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J55" s="4">
         <v>8</v>
@@ -5335,19 +5329,19 @@
     </row>
     <row r="56" spans="1:15">
       <c r="A56" s="4" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D56" s="13">
         <v>1</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F56" s="13">
         <v>1</v>
@@ -5359,60 +5353,60 @@
         <v>2</v>
       </c>
       <c r="I56" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J56" s="4">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>11</v>
+        <v>124</v>
       </c>
       <c r="L56" s="4" t="s">
         <v>13</v>
       </c>
       <c r="M56" s="4">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="N56" s="4">
         <v>1</v>
       </c>
       <c r="O56" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:15">
       <c r="A57" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D57" s="13">
         <v>1</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F57" s="13">
         <v>1</v>
       </c>
       <c r="G57" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I57" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J57" s="4">
         <v>21</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L57" s="4" t="s">
         <v>13</v>
@@ -5429,37 +5423,37 @@
     </row>
     <row r="58" spans="1:15">
       <c r="A58" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D58" s="13">
         <v>1</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F58" s="13">
         <v>1</v>
       </c>
       <c r="G58" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H58" s="13">
         <v>1</v>
       </c>
       <c r="I58" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J58" s="4">
         <v>21</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L58" s="4" t="s">
         <v>13</v>
@@ -5476,37 +5470,34 @@
     </row>
     <row r="59" spans="1:15">
       <c r="A59" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D59" s="13">
-        <v>1</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>399</v>
+        <v>0</v>
       </c>
       <c r="F59" s="13">
         <v>1</v>
       </c>
       <c r="G59" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H59" s="13">
         <v>1</v>
       </c>
       <c r="I59" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J59" s="4">
         <v>21</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L59" s="4" t="s">
         <v>13</v>
@@ -5523,34 +5514,37 @@
     </row>
     <row r="60" spans="1:15">
       <c r="A60" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D60" s="13">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>397</v>
       </c>
       <c r="F60" s="13">
         <v>1</v>
       </c>
       <c r="G60" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H60" s="13">
         <v>1</v>
       </c>
       <c r="I60" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J60" s="4">
         <v>21</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L60" s="4" t="s">
         <v>13</v>
@@ -5567,37 +5561,34 @@
     </row>
     <row r="61" spans="1:15">
       <c r="A61" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D61" s="13">
-        <v>1</v>
-      </c>
-      <c r="E61" s="13" t="s">
-        <v>399</v>
+        <v>0</v>
       </c>
       <c r="F61" s="13">
         <v>1</v>
       </c>
       <c r="G61" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H61" s="13">
         <v>1</v>
       </c>
       <c r="I61" s="4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J61" s="4">
         <v>21</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L61" s="4" t="s">
         <v>13</v>
@@ -5614,13 +5605,13 @@
     </row>
     <row r="62" spans="1:15">
       <c r="A62" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D62" s="13">
         <v>0</v>
@@ -5629,19 +5620,19 @@
         <v>1</v>
       </c>
       <c r="G62" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H62" s="13">
         <v>1</v>
       </c>
       <c r="I62" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J62" s="4">
         <v>21</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L62" s="4" t="s">
         <v>13</v>
@@ -5658,34 +5649,37 @@
     </row>
     <row r="63" spans="1:15">
       <c r="A63" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D63" s="13">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>397</v>
       </c>
       <c r="F63" s="13">
         <v>1</v>
       </c>
       <c r="G63" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63" s="13">
         <v>1</v>
       </c>
       <c r="I63" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J63" s="4">
         <v>21</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L63" s="4" t="s">
         <v>13</v>
@@ -5702,13 +5696,13 @@
     </row>
     <row r="64" spans="1:15">
       <c r="A64" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D64" s="13">
         <v>1</v>
@@ -5720,19 +5714,19 @@
         <v>1</v>
       </c>
       <c r="G64" s="13">
+        <v>1</v>
+      </c>
+      <c r="H64" s="13">
         <v>2</v>
       </c>
-      <c r="H64" s="13">
-        <v>1</v>
-      </c>
       <c r="I64" s="4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J64" s="4">
         <v>21</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L64" s="4" t="s">
         <v>13</v>
@@ -5749,37 +5743,37 @@
     </row>
     <row r="65" spans="1:15">
       <c r="A65" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D65" s="13">
         <v>1</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F65" s="13">
         <v>1</v>
       </c>
       <c r="G65" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I65" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J65" s="4">
         <v>21</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L65" s="4" t="s">
         <v>13</v>
@@ -5796,37 +5790,37 @@
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>136</v>
+        <v>146</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="D66" s="13">
         <v>1</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F66" s="13">
         <v>1</v>
       </c>
       <c r="G66" s="13">
+        <v>1</v>
+      </c>
+      <c r="H66" s="13">
         <v>2</v>
       </c>
-      <c r="H66" s="13">
-        <v>1</v>
-      </c>
       <c r="I66" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J66" s="4">
         <v>21</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L66" s="4" t="s">
         <v>13</v>
@@ -5843,19 +5837,19 @@
     </row>
     <row r="67" spans="1:15">
       <c r="A67" s="4" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="B67" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C67" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="C67" s="6" t="s">
-        <v>137</v>
-      </c>
       <c r="D67" s="13">
         <v>1</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F67" s="13">
         <v>1</v>
@@ -5867,19 +5861,19 @@
         <v>2</v>
       </c>
       <c r="I67" s="4">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J67" s="4">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L67" s="4" t="s">
         <v>13</v>
       </c>
       <c r="M67" s="4">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="N67" s="4">
         <v>1</v>
@@ -5890,37 +5884,37 @@
     </row>
     <row r="68" spans="1:15">
       <c r="A68" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C68" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="B68" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>150</v>
-      </c>
       <c r="D68" s="13">
         <v>1</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F68" s="13">
         <v>1</v>
       </c>
       <c r="G68" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I68" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J68" s="4">
         <v>25</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L68" s="4" t="s">
         <v>13</v>
@@ -5937,37 +5931,37 @@
     </row>
     <row r="69" spans="1:15">
       <c r="A69" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D69" s="13">
         <v>1</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F69" s="13">
         <v>1</v>
       </c>
       <c r="G69" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H69" s="13">
         <v>1</v>
       </c>
       <c r="I69" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J69" s="4">
         <v>25</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L69" s="4" t="s">
         <v>13</v>
@@ -5984,37 +5978,37 @@
     </row>
     <row r="70" spans="1:15">
       <c r="A70" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D70" s="13">
         <v>1</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F70" s="13">
         <v>1</v>
       </c>
       <c r="G70" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H70" s="13">
         <v>1</v>
       </c>
       <c r="I70" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J70" s="4">
         <v>25</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L70" s="4" t="s">
         <v>13</v>
@@ -6031,37 +6025,37 @@
     </row>
     <row r="71" spans="1:15">
       <c r="A71" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D71" s="13">
         <v>1</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F71" s="13">
         <v>1</v>
       </c>
       <c r="G71" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H71" s="13">
         <v>1</v>
       </c>
       <c r="I71" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J71" s="4">
         <v>25</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L71" s="4" t="s">
         <v>13</v>
@@ -6078,37 +6072,34 @@
     </row>
     <row r="72" spans="1:15">
       <c r="A72" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D72" s="13">
-        <v>1</v>
-      </c>
-      <c r="E72" s="13" t="s">
-        <v>399</v>
+        <v>0</v>
       </c>
       <c r="F72" s="13">
         <v>1</v>
       </c>
       <c r="G72" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H72" s="13">
         <v>1</v>
       </c>
       <c r="I72" s="4">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J72" s="4">
         <v>25</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L72" s="4" t="s">
         <v>13</v>
@@ -6125,13 +6116,13 @@
     </row>
     <row r="73" spans="1:15">
       <c r="A73" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D73" s="13">
         <v>0</v>
@@ -6140,19 +6131,19 @@
         <v>1</v>
       </c>
       <c r="G73" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H73" s="13">
         <v>1</v>
       </c>
       <c r="I73" s="4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J73" s="4">
         <v>25</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L73" s="4" t="s">
         <v>13</v>
@@ -6169,13 +6160,13 @@
     </row>
     <row r="74" spans="1:15">
       <c r="A74" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D74" s="13">
         <v>0</v>
@@ -6184,19 +6175,19 @@
         <v>1</v>
       </c>
       <c r="G74" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H74" s="13">
         <v>1</v>
       </c>
       <c r="I74" s="4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J74" s="4">
         <v>25</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L74" s="4" t="s">
         <v>13</v>
@@ -6213,34 +6204,37 @@
     </row>
     <row r="75" spans="1:15">
       <c r="A75" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D75" s="13">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>397</v>
       </c>
       <c r="F75" s="13">
         <v>1</v>
       </c>
       <c r="G75" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H75" s="13">
         <v>1</v>
       </c>
       <c r="I75" s="4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J75" s="4">
         <v>25</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L75" s="4" t="s">
         <v>13</v>
@@ -6257,13 +6251,13 @@
     </row>
     <row r="76" spans="1:15">
       <c r="A76" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>158</v>
+        <v>168</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>391</v>
       </c>
       <c r="D76" s="13">
         <v>1</v>
@@ -6275,19 +6269,19 @@
         <v>1</v>
       </c>
       <c r="G76" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H76" s="13">
         <v>1</v>
       </c>
       <c r="I76" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J76" s="4">
         <v>25</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L76" s="4" t="s">
         <v>13</v>
@@ -6304,37 +6298,37 @@
     </row>
     <row r="77" spans="1:15">
       <c r="A77" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>393</v>
+        <v>157</v>
       </c>
       <c r="D77" s="13">
         <v>1</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F77" s="13">
         <v>1</v>
       </c>
       <c r="G77" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H77" s="13">
         <v>1</v>
       </c>
       <c r="I77" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J77" s="4">
         <v>25</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L77" s="4" t="s">
         <v>13</v>
@@ -6351,37 +6345,37 @@
     </row>
     <row r="78" spans="1:15">
       <c r="A78" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C78" s="10" t="s">
-        <v>159</v>
+        <v>170</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>158</v>
       </c>
       <c r="D78" s="13">
         <v>1</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F78" s="13">
         <v>1</v>
       </c>
       <c r="G78" s="13">
+        <v>1</v>
+      </c>
+      <c r="H78" s="13">
         <v>2</v>
       </c>
-      <c r="H78" s="13">
-        <v>1</v>
-      </c>
       <c r="I78" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J78" s="4">
         <v>25</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L78" s="4" t="s">
         <v>13</v>
@@ -6398,19 +6392,19 @@
     </row>
     <row r="79" spans="1:15">
       <c r="A79" s="4" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="B79" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C79" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="C79" s="9" t="s">
-        <v>160</v>
-      </c>
       <c r="D79" s="13">
         <v>1</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F79" s="13">
         <v>1</v>
@@ -6422,60 +6416,60 @@
         <v>2</v>
       </c>
       <c r="I79" s="4">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="J79" s="4">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L79" s="4" t="s">
         <v>13</v>
       </c>
       <c r="M79" s="4">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="N79" s="4">
         <v>1</v>
       </c>
       <c r="O79" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:15">
       <c r="A80" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>174</v>
+        <v>400</v>
       </c>
       <c r="D80" s="13">
         <v>1</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F80" s="13">
         <v>1</v>
       </c>
       <c r="G80" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I80" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J80" s="4">
         <v>16</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L80" s="4" t="s">
         <v>13</v>
@@ -6492,37 +6486,37 @@
     </row>
     <row r="81" spans="1:15">
       <c r="A81" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C81" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B81" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="C81" s="9" t="s">
-        <v>402</v>
-      </c>
       <c r="D81" s="13">
         <v>1</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F81" s="13">
         <v>1</v>
       </c>
       <c r="G81" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H81" s="13">
         <v>1</v>
       </c>
       <c r="I81" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J81" s="4">
         <v>16</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L81" s="4" t="s">
         <v>13</v>
@@ -6539,37 +6533,37 @@
     </row>
     <row r="82" spans="1:15">
       <c r="A82" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D82" s="13">
         <v>1</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F82" s="13">
         <v>1</v>
       </c>
       <c r="G82" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H82" s="13">
         <v>1</v>
       </c>
       <c r="I82" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J82" s="4">
         <v>16</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L82" s="4" t="s">
         <v>13</v>
@@ -6586,13 +6580,13 @@
     </row>
     <row r="83" spans="1:15">
       <c r="A83" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D83" s="13">
         <v>1</v>
@@ -6604,19 +6598,19 @@
         <v>1</v>
       </c>
       <c r="G83" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H83" s="13">
         <v>1</v>
       </c>
       <c r="I83" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J83" s="4">
         <v>16</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L83" s="4" t="s">
         <v>13</v>
@@ -6633,37 +6627,37 @@
     </row>
     <row r="84" spans="1:15">
       <c r="A84" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D84" s="13">
         <v>1</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F84" s="13">
         <v>1</v>
       </c>
       <c r="G84" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H84" s="13">
         <v>1</v>
       </c>
       <c r="I84" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J84" s="4">
         <v>16</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L84" s="4" t="s">
         <v>13</v>
@@ -6680,13 +6674,13 @@
     </row>
     <row r="85" spans="1:15">
       <c r="A85" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D85" s="13">
         <v>1</v>
@@ -6698,19 +6692,19 @@
         <v>1</v>
       </c>
       <c r="G85" s="13">
+        <v>1</v>
+      </c>
+      <c r="H85" s="13">
         <v>2</v>
       </c>
-      <c r="H85" s="13">
-        <v>1</v>
-      </c>
       <c r="I85" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J85" s="4">
         <v>16</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L85" s="4" t="s">
         <v>13</v>
@@ -6727,37 +6721,37 @@
     </row>
     <row r="86" spans="1:15">
       <c r="A86" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D86" s="13">
         <v>1</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F86" s="13">
         <v>1</v>
       </c>
       <c r="G86" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I86" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J86" s="4">
         <v>16</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L86" s="4" t="s">
         <v>13</v>
@@ -6774,37 +6768,34 @@
     </row>
     <row r="87" spans="1:15">
       <c r="A87" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D87" s="13">
-        <v>1</v>
-      </c>
-      <c r="E87" s="13" t="s">
-        <v>399</v>
+        <v>0</v>
       </c>
       <c r="F87" s="13">
         <v>1</v>
       </c>
       <c r="G87" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H87" s="13">
         <v>1</v>
       </c>
       <c r="I87" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J87" s="4">
         <v>16</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L87" s="4" t="s">
         <v>13</v>
@@ -6821,13 +6812,13 @@
     </row>
     <row r="88" spans="1:15">
       <c r="A88" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D88" s="13">
         <v>0</v>
@@ -6836,19 +6827,19 @@
         <v>1</v>
       </c>
       <c r="G88" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H88" s="13">
         <v>1</v>
       </c>
       <c r="I88" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J88" s="4">
         <v>16</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L88" s="4" t="s">
         <v>13</v>
@@ -6865,40 +6856,43 @@
     </row>
     <row r="89" spans="1:15">
       <c r="A89" s="4" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C89" s="9" t="s">
-        <v>182</v>
+        <v>204</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>196</v>
       </c>
       <c r="D89" s="13">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>399</v>
       </c>
       <c r="F89" s="13">
         <v>1</v>
       </c>
       <c r="G89" s="13">
+        <v>0</v>
+      </c>
+      <c r="H89" s="13">
+        <v>1</v>
+      </c>
+      <c r="I89" s="4">
         <v>2</v>
       </c>
-      <c r="H89" s="13">
-        <v>1</v>
-      </c>
-      <c r="I89" s="4">
-        <v>16</v>
-      </c>
       <c r="J89" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L89" s="4" t="s">
         <v>13</v>
       </c>
       <c r="M89" s="4">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="N89" s="4">
         <v>1</v>
@@ -6909,37 +6903,37 @@
     </row>
     <row r="90" spans="1:15">
       <c r="A90" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>198</v>
+        <v>401</v>
       </c>
       <c r="D90" s="13">
         <v>1</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F90" s="13">
         <v>1</v>
       </c>
       <c r="G90" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H90" s="13">
         <v>1</v>
       </c>
       <c r="I90" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J90" s="4">
         <v>17</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L90" s="4" t="s">
         <v>13</v>
@@ -6956,37 +6950,37 @@
     </row>
     <row r="91" spans="1:15">
       <c r="A91" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>403</v>
+        <v>197</v>
       </c>
       <c r="D91" s="13">
         <v>1</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F91" s="13">
         <v>1</v>
       </c>
       <c r="G91" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H91" s="13">
         <v>1</v>
       </c>
       <c r="I91" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J91" s="4">
         <v>17</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L91" s="4" t="s">
         <v>13</v>
@@ -7003,37 +6997,37 @@
     </row>
     <row r="92" spans="1:15">
       <c r="A92" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D92" s="13">
         <v>1</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F92" s="13">
         <v>1</v>
       </c>
       <c r="G92" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H92" s="13">
         <v>1</v>
       </c>
       <c r="I92" s="4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J92" s="4">
         <v>17</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L92" s="4" t="s">
         <v>13</v>
@@ -7050,37 +7044,37 @@
     </row>
     <row r="93" spans="1:15">
       <c r="A93" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>200</v>
+        <v>156</v>
       </c>
       <c r="D93" s="13">
         <v>1</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F93" s="13">
         <v>1</v>
       </c>
       <c r="G93" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H93" s="13">
         <v>1</v>
       </c>
       <c r="I93" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J93" s="4">
         <v>17</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L93" s="4" t="s">
         <v>13</v>
@@ -7097,13 +7091,13 @@
     </row>
     <row r="94" spans="1:15">
       <c r="A94" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="D94" s="13">
         <v>1</v>
@@ -7115,19 +7109,19 @@
         <v>1</v>
       </c>
       <c r="G94" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H94" s="13">
         <v>1</v>
       </c>
       <c r="I94" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J94" s="4">
         <v>17</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L94" s="4" t="s">
         <v>13</v>
@@ -7144,37 +7138,37 @@
     </row>
     <row r="95" spans="1:15">
       <c r="A95" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D95" s="13">
         <v>1</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F95" s="13">
         <v>1</v>
       </c>
       <c r="G95" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H95" s="13">
         <v>1</v>
       </c>
       <c r="I95" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J95" s="4">
         <v>17</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L95" s="4" t="s">
         <v>13</v>
@@ -7191,37 +7185,37 @@
     </row>
     <row r="96" spans="1:15">
       <c r="A96" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="D96" s="13">
         <v>1</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F96" s="13">
         <v>1</v>
       </c>
       <c r="G96" s="13">
+        <v>1</v>
+      </c>
+      <c r="H96" s="13">
         <v>2</v>
       </c>
-      <c r="H96" s="13">
-        <v>1</v>
-      </c>
       <c r="I96" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J96" s="4">
         <v>17</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L96" s="4" t="s">
         <v>13</v>
@@ -7238,37 +7232,37 @@
     </row>
     <row r="97" spans="1:15">
       <c r="A97" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="D97" s="13">
         <v>1</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F97" s="13">
         <v>1</v>
       </c>
       <c r="G97" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I97" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J97" s="4">
         <v>17</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L97" s="4" t="s">
         <v>13</v>
@@ -7285,37 +7279,34 @@
     </row>
     <row r="98" spans="1:15">
       <c r="A98" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D98" s="13">
-        <v>1</v>
-      </c>
-      <c r="E98" s="13" t="s">
-        <v>399</v>
+        <v>0</v>
       </c>
       <c r="F98" s="13">
         <v>1</v>
       </c>
       <c r="G98" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H98" s="13">
         <v>1</v>
       </c>
       <c r="I98" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J98" s="4">
         <v>17</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L98" s="4" t="s">
         <v>13</v>
@@ -7332,13 +7323,13 @@
     </row>
     <row r="99" spans="1:15">
       <c r="A99" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D99" s="13">
         <v>0</v>
@@ -7347,19 +7338,19 @@
         <v>1</v>
       </c>
       <c r="G99" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H99" s="13">
         <v>1</v>
       </c>
       <c r="I99" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J99" s="4">
         <v>17</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L99" s="4" t="s">
         <v>13</v>
@@ -7376,40 +7367,43 @@
     </row>
     <row r="100" spans="1:15">
       <c r="A100" s="4" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="D100" s="13">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E100" s="13" t="s">
+        <v>397</v>
       </c>
       <c r="F100" s="13">
         <v>1</v>
       </c>
       <c r="G100" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H100" s="13">
         <v>1</v>
       </c>
       <c r="I100" s="4">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J100" s="4">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L100" s="4" t="s">
         <v>13</v>
       </c>
       <c r="M100" s="4">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="N100" s="4">
         <v>1</v>
@@ -7420,37 +7414,37 @@
     </row>
     <row r="101" spans="1:15">
       <c r="A101" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C101" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="B101" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="C101" s="11" t="s">
-        <v>220</v>
-      </c>
       <c r="D101" s="13">
         <v>1</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F101" s="13">
         <v>1</v>
       </c>
       <c r="G101" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H101" s="13">
         <v>1</v>
       </c>
       <c r="I101" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J101" s="4">
         <v>22</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L101" s="4" t="s">
         <v>13</v>
@@ -7467,37 +7461,37 @@
     </row>
     <row r="102" spans="1:15">
       <c r="A102" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D102" s="13">
         <v>1</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F102" s="13">
         <v>1</v>
       </c>
       <c r="G102" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H102" s="13">
         <v>1</v>
       </c>
       <c r="I102" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J102" s="4">
         <v>22</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L102" s="4" t="s">
         <v>13</v>
@@ -7514,37 +7508,37 @@
     </row>
     <row r="103" spans="1:15">
       <c r="A103" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D103" s="13">
         <v>1</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F103" s="13">
         <v>1</v>
       </c>
       <c r="G103" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H103" s="13">
         <v>1</v>
       </c>
       <c r="I103" s="4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J103" s="4">
         <v>22</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L103" s="4" t="s">
         <v>13</v>
@@ -7561,37 +7555,37 @@
     </row>
     <row r="104" spans="1:15">
       <c r="A104" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D104" s="13">
         <v>1</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="F104" s="13">
         <v>1</v>
       </c>
       <c r="G104" s="13">
+        <v>1</v>
+      </c>
+      <c r="H104" s="13">
         <v>2</v>
       </c>
-      <c r="H104" s="13">
-        <v>1</v>
-      </c>
       <c r="I104" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J104" s="4">
         <v>22</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L104" s="4" t="s">
         <v>13</v>
@@ -7608,13 +7602,13 @@
     </row>
     <row r="105" spans="1:15">
       <c r="A105" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="C105" s="11" t="s">
-        <v>224</v>
+        <v>234</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>223</v>
       </c>
       <c r="D105" s="13">
         <v>1</v>
@@ -7626,19 +7620,19 @@
         <v>1</v>
       </c>
       <c r="G105" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H105" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I105" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J105" s="4">
         <v>22</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L105" s="4" t="s">
         <v>13</v>
@@ -7655,13 +7649,13 @@
     </row>
     <row r="106" spans="1:15">
       <c r="A106" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D106" s="13">
         <v>1</v>
@@ -7673,19 +7667,19 @@
         <v>1</v>
       </c>
       <c r="G106" s="13">
+        <v>1</v>
+      </c>
+      <c r="H106" s="13">
         <v>2</v>
       </c>
-      <c r="H106" s="13">
-        <v>1</v>
-      </c>
       <c r="I106" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J106" s="4">
         <v>22</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L106" s="4" t="s">
         <v>13</v>
@@ -7702,37 +7696,37 @@
     </row>
     <row r="107" spans="1:15">
       <c r="A107" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D107" s="13">
         <v>1</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F107" s="13">
         <v>1</v>
       </c>
       <c r="G107" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H107" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I107" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J107" s="4">
         <v>22</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L107" s="4" t="s">
         <v>13</v>
@@ -7749,37 +7743,37 @@
     </row>
     <row r="108" spans="1:15">
       <c r="A108" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D108" s="13">
         <v>1</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F108" s="13">
         <v>1</v>
       </c>
       <c r="G108" s="13">
+        <v>1</v>
+      </c>
+      <c r="H108" s="13">
         <v>2</v>
       </c>
-      <c r="H108" s="13">
-        <v>1</v>
-      </c>
       <c r="I108" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J108" s="4">
         <v>22</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L108" s="4" t="s">
         <v>13</v>
@@ -7796,37 +7790,37 @@
     </row>
     <row r="109" spans="1:15">
       <c r="A109" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D109" s="13">
         <v>1</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F109" s="13">
         <v>1</v>
       </c>
       <c r="G109" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H109" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I109" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J109" s="4">
         <v>22</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L109" s="4" t="s">
         <v>13</v>
@@ -7843,37 +7837,34 @@
     </row>
     <row r="110" spans="1:15">
       <c r="A110" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>229</v>
+        <v>402</v>
       </c>
       <c r="D110" s="13">
-        <v>1</v>
-      </c>
-      <c r="E110" s="13" t="s">
-        <v>399</v>
+        <v>0</v>
       </c>
       <c r="F110" s="13">
         <v>1</v>
       </c>
       <c r="G110" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H110" s="13">
         <v>1</v>
       </c>
       <c r="I110" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J110" s="4">
         <v>22</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L110" s="4" t="s">
         <v>13</v>
@@ -7890,13 +7881,13 @@
     </row>
     <row r="111" spans="1:15">
       <c r="A111" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>404</v>
+        <v>228</v>
       </c>
       <c r="D111" s="13">
         <v>0</v>
@@ -7905,19 +7896,19 @@
         <v>1</v>
       </c>
       <c r="G111" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H111" s="13">
         <v>1</v>
       </c>
       <c r="I111" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J111" s="4">
         <v>22</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L111" s="4" t="s">
         <v>13</v>
@@ -7934,40 +7925,43 @@
     </row>
     <row r="112" spans="1:15">
       <c r="A112" s="4" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>230</v>
+        <v>403</v>
       </c>
       <c r="D112" s="13">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>397</v>
       </c>
       <c r="F112" s="13">
         <v>1</v>
       </c>
       <c r="G112" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H112" s="13">
         <v>1</v>
       </c>
       <c r="I112" s="4">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J112" s="4">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L112" s="4" t="s">
         <v>13</v>
       </c>
       <c r="M112" s="4">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="N112" s="4">
         <v>1</v>
@@ -7978,37 +7972,37 @@
     </row>
     <row r="113" spans="1:16">
       <c r="A113" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>405</v>
+        <v>219</v>
       </c>
       <c r="D113" s="13">
         <v>1</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F113" s="13">
         <v>1</v>
       </c>
       <c r="G113" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H113" s="13">
         <v>1</v>
       </c>
       <c r="I113" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J113" s="4">
         <v>29</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L113" s="4" t="s">
         <v>13</v>
@@ -8025,37 +8019,37 @@
     </row>
     <row r="114" spans="1:16">
       <c r="A114" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D114" s="13">
         <v>1</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F114" s="13">
         <v>1</v>
       </c>
       <c r="G114" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H114" s="13">
         <v>1</v>
       </c>
       <c r="I114" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J114" s="4">
         <v>29</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L114" s="4" t="s">
         <v>13</v>
@@ -8072,37 +8066,37 @@
     </row>
     <row r="115" spans="1:16">
       <c r="A115" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="D115" s="13">
         <v>1</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F115" s="13">
         <v>1</v>
       </c>
       <c r="G115" s="13">
+        <v>1</v>
+      </c>
+      <c r="H115" s="13">
         <v>2</v>
       </c>
-      <c r="H115" s="13">
-        <v>1</v>
-      </c>
       <c r="I115" s="4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J115" s="4">
         <v>29</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L115" s="4" t="s">
         <v>13</v>
@@ -8119,37 +8113,37 @@
     </row>
     <row r="116" spans="1:16">
       <c r="A116" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C116" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="B116" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="C116" s="9" t="s">
-        <v>244</v>
-      </c>
       <c r="D116" s="13">
         <v>1</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F116" s="13">
         <v>1</v>
       </c>
       <c r="G116" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H116" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I116" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J116" s="4">
         <v>29</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L116" s="4" t="s">
         <v>13</v>
@@ -8166,37 +8160,37 @@
     </row>
     <row r="117" spans="1:16">
       <c r="A117" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D117" s="13">
         <v>1</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="F117" s="13">
         <v>1</v>
       </c>
       <c r="G117" s="13">
+        <v>1</v>
+      </c>
+      <c r="H117" s="13">
         <v>2</v>
       </c>
-      <c r="H117" s="13">
-        <v>1</v>
-      </c>
       <c r="I117" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J117" s="4">
         <v>29</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L117" s="4" t="s">
         <v>13</v>
@@ -8213,13 +8207,13 @@
     </row>
     <row r="118" spans="1:16">
       <c r="A118" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D118" s="13">
         <v>1</v>
@@ -8231,19 +8225,19 @@
         <v>1</v>
       </c>
       <c r="G118" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I118" s="4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J118" s="4">
         <v>29</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L118" s="4" t="s">
         <v>13</v>
@@ -8260,37 +8254,37 @@
     </row>
     <row r="119" spans="1:16">
       <c r="A119" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D119" s="13">
         <v>1</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F119" s="13">
         <v>1</v>
       </c>
       <c r="G119" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H119" s="13">
         <v>1</v>
       </c>
       <c r="I119" s="4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J119" s="4">
         <v>29</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L119" s="4" t="s">
         <v>13</v>
@@ -8307,13 +8301,13 @@
     </row>
     <row r="120" spans="1:16">
       <c r="A120" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D120" s="13">
         <v>1</v>
@@ -8325,19 +8319,19 @@
         <v>1</v>
       </c>
       <c r="G120" s="13">
+        <v>1</v>
+      </c>
+      <c r="H120" s="13">
         <v>2</v>
       </c>
-      <c r="H120" s="13">
-        <v>1</v>
-      </c>
       <c r="I120" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J120" s="4">
         <v>29</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L120" s="4" t="s">
         <v>13</v>
@@ -8354,19 +8348,19 @@
     </row>
     <row r="121" spans="1:16">
       <c r="A121" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D121" s="13">
         <v>1</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F121" s="13">
         <v>1</v>
@@ -8378,13 +8372,13 @@
         <v>2</v>
       </c>
       <c r="I121" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J121" s="4">
         <v>29</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L121" s="4" t="s">
         <v>13</v>
@@ -8401,37 +8395,37 @@
     </row>
     <row r="122" spans="1:16">
       <c r="A122" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D122" s="13">
         <v>1</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F122" s="13">
         <v>1</v>
       </c>
       <c r="G122" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H122" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I122" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J122" s="4">
         <v>29</v>
       </c>
       <c r="K122" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L122" s="4" t="s">
         <v>13</v>
@@ -8448,13 +8442,13 @@
     </row>
     <row r="123" spans="1:16">
       <c r="A123" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D123" s="13">
         <v>1</v>
@@ -8466,19 +8460,19 @@
         <v>1</v>
       </c>
       <c r="G123" s="13">
+        <v>1</v>
+      </c>
+      <c r="H123" s="13">
         <v>2</v>
       </c>
-      <c r="H123" s="13">
-        <v>1</v>
-      </c>
       <c r="I123" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J123" s="4">
         <v>29</v>
       </c>
       <c r="K123" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L123" s="4" t="s">
         <v>13</v>
@@ -8495,37 +8489,37 @@
     </row>
     <row r="124" spans="1:16">
       <c r="A124" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D124" s="13">
         <v>1</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F124" s="13">
         <v>1</v>
       </c>
       <c r="G124" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H124" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I124" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J124" s="4">
         <v>29</v>
       </c>
       <c r="K124" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L124" s="4" t="s">
         <v>13</v>
@@ -8542,37 +8536,34 @@
     </row>
     <row r="125" spans="1:16">
       <c r="A125" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>253</v>
+        <v>404</v>
       </c>
       <c r="D125" s="13">
-        <v>1</v>
-      </c>
-      <c r="E125" s="13" t="s">
-        <v>399</v>
+        <v>0</v>
       </c>
       <c r="F125" s="13">
         <v>1</v>
       </c>
       <c r="G125" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H125" s="13">
         <v>1</v>
       </c>
       <c r="I125" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J125" s="4">
         <v>29</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L125" s="4" t="s">
         <v>13</v>
@@ -8589,13 +8580,13 @@
     </row>
     <row r="126" spans="1:16">
       <c r="A126" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>406</v>
+        <v>252</v>
       </c>
       <c r="D126" s="13">
         <v>0</v>
@@ -8604,19 +8595,19 @@
         <v>1</v>
       </c>
       <c r="G126" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H126" s="13">
         <v>1</v>
       </c>
       <c r="I126" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J126" s="4">
         <v>29</v>
       </c>
       <c r="K126" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L126" s="4" t="s">
         <v>13</v>
@@ -8633,40 +8624,43 @@
     </row>
     <row r="127" spans="1:16">
       <c r="A127" s="4" t="s">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="D127" s="13">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E127" s="13" t="s">
+        <v>399</v>
       </c>
       <c r="F127" s="13">
         <v>1</v>
       </c>
       <c r="G127" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H127" s="13">
         <v>1</v>
       </c>
       <c r="I127" s="4">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="J127" s="4">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K127" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L127" s="4" t="s">
         <v>13</v>
       </c>
       <c r="M127" s="4">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="N127" s="4">
         <v>1</v>
@@ -8674,40 +8668,41 @@
       <c r="O127" s="4">
         <v>1</v>
       </c>
+      <c r="P127" s="4"/>
     </row>
     <row r="128" spans="1:16">
       <c r="A128" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="C128" s="9" t="s">
-        <v>279</v>
+      <c r="C128" s="14" t="s">
+        <v>405</v>
       </c>
       <c r="D128" s="13">
         <v>1</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F128" s="13">
         <v>1</v>
       </c>
       <c r="G128" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H128" s="13">
         <v>1</v>
       </c>
       <c r="I128" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J128" s="4">
         <v>38</v>
       </c>
       <c r="K128" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L128" s="4" t="s">
         <v>13</v>
@@ -8725,37 +8720,37 @@
     </row>
     <row r="129" spans="1:16">
       <c r="A129" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B129" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C129" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="C129" s="14" t="s">
-        <v>407</v>
-      </c>
       <c r="D129" s="13">
         <v>1</v>
       </c>
       <c r="E129" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F129" s="13">
         <v>1</v>
       </c>
       <c r="G129" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H129" s="13">
         <v>1</v>
       </c>
       <c r="I129" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J129" s="4">
         <v>38</v>
       </c>
       <c r="K129" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L129" s="4" t="s">
         <v>13</v>
@@ -8773,7 +8768,7 @@
     </row>
     <row r="130" spans="1:16">
       <c r="A130" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>281</v>
@@ -8785,25 +8780,25 @@
         <v>1</v>
       </c>
       <c r="E130" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F130" s="13">
         <v>1</v>
       </c>
       <c r="G130" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H130" s="13">
         <v>1</v>
       </c>
       <c r="I130" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J130" s="4">
         <v>38</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L130" s="4" t="s">
         <v>13</v>
@@ -8821,7 +8816,7 @@
     </row>
     <row r="131" spans="1:16">
       <c r="A131" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>283</v>
@@ -8833,25 +8828,25 @@
         <v>1</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F131" s="13">
         <v>1</v>
       </c>
       <c r="G131" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H131" s="13">
         <v>1</v>
       </c>
       <c r="I131" s="4">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J131" s="4">
         <v>38</v>
       </c>
       <c r="K131" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L131" s="4" t="s">
         <v>13</v>
@@ -8869,37 +8864,37 @@
     </row>
     <row r="132" spans="1:16">
       <c r="A132" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C132" s="9" t="s">
+      <c r="C132" s="14" t="s">
         <v>286</v>
       </c>
       <c r="D132" s="13">
         <v>1</v>
       </c>
       <c r="E132" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F132" s="13">
         <v>1</v>
       </c>
       <c r="G132" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H132" s="13">
         <v>1</v>
       </c>
       <c r="I132" s="4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J132" s="4">
         <v>38</v>
       </c>
       <c r="K132" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L132" s="4" t="s">
         <v>13</v>
@@ -8917,7 +8912,7 @@
     </row>
     <row r="133" spans="1:16">
       <c r="A133" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>287</v>
@@ -8929,25 +8924,25 @@
         <v>1</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="F133" s="13">
         <v>1</v>
       </c>
       <c r="G133" s="13">
+        <v>1</v>
+      </c>
+      <c r="H133" s="13">
         <v>2</v>
       </c>
-      <c r="H133" s="13">
-        <v>1</v>
-      </c>
       <c r="I133" s="4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J133" s="4">
         <v>38</v>
       </c>
       <c r="K133" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L133" s="4" t="s">
         <v>13</v>
@@ -8965,7 +8960,7 @@
     </row>
     <row r="134" spans="1:16">
       <c r="A134" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B134" s="4" t="s">
         <v>289</v>
@@ -8977,7 +8972,7 @@
         <v>1</v>
       </c>
       <c r="E134" s="13" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F134" s="13">
         <v>1</v>
@@ -8989,13 +8984,13 @@
         <v>2</v>
       </c>
       <c r="I134" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J134" s="4">
         <v>38</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L134" s="4" t="s">
         <v>13</v>
@@ -9013,7 +9008,7 @@
     </row>
     <row r="135" spans="1:16">
       <c r="A135" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>291</v>
@@ -9031,19 +9026,19 @@
         <v>1</v>
       </c>
       <c r="G135" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H135" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I135" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J135" s="4">
         <v>38</v>
       </c>
       <c r="K135" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L135" s="4" t="s">
         <v>13</v>
@@ -9061,7 +9056,7 @@
     </row>
     <row r="136" spans="1:16">
       <c r="A136" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>293</v>
@@ -9079,19 +9074,19 @@
         <v>1</v>
       </c>
       <c r="G136" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H136" s="13">
         <v>1</v>
       </c>
       <c r="I136" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J136" s="4">
         <v>38</v>
       </c>
       <c r="K136" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L136" s="4" t="s">
         <v>13</v>
@@ -9109,7 +9104,7 @@
     </row>
     <row r="137" spans="1:16">
       <c r="A137" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>295</v>
@@ -9121,25 +9116,25 @@
         <v>1</v>
       </c>
       <c r="E137" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F137" s="13">
         <v>1</v>
       </c>
       <c r="G137" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H137" s="13">
         <v>1</v>
       </c>
       <c r="I137" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J137" s="4">
         <v>38</v>
       </c>
       <c r="K137" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L137" s="4" t="s">
         <v>13</v>
@@ -9157,7 +9152,7 @@
     </row>
     <row r="138" spans="1:16">
       <c r="A138" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>297</v>
@@ -9169,25 +9164,25 @@
         <v>1</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F138" s="13">
         <v>1</v>
       </c>
       <c r="G138" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H138" s="13">
         <v>1</v>
       </c>
       <c r="I138" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J138" s="4">
         <v>38</v>
       </c>
       <c r="K138" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L138" s="4" t="s">
         <v>13</v>
@@ -9205,7 +9200,7 @@
     </row>
     <row r="139" spans="1:16">
       <c r="A139" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>299</v>
@@ -9223,19 +9218,19 @@
         <v>1</v>
       </c>
       <c r="G139" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H139" s="13">
         <v>1</v>
       </c>
       <c r="I139" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J139" s="4">
         <v>38</v>
       </c>
       <c r="K139" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L139" s="4" t="s">
         <v>13</v>
@@ -9253,37 +9248,37 @@
     </row>
     <row r="140" spans="1:16">
       <c r="A140" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B140" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="C140" s="14" t="s">
+      <c r="C140" s="9" t="s">
         <v>302</v>
       </c>
       <c r="D140" s="13">
         <v>1</v>
       </c>
       <c r="E140" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F140" s="13">
         <v>1</v>
       </c>
       <c r="G140" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H140" s="13">
         <v>1</v>
       </c>
       <c r="I140" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J140" s="4">
         <v>38</v>
       </c>
       <c r="K140" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L140" s="4" t="s">
         <v>13</v>
@@ -9301,37 +9296,37 @@
     </row>
     <row r="141" spans="1:16">
       <c r="A141" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="C141" s="9" t="s">
+      <c r="C141" s="14" t="s">
         <v>304</v>
       </c>
       <c r="D141" s="13">
         <v>1</v>
       </c>
       <c r="E141" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F141" s="13">
         <v>1</v>
       </c>
       <c r="G141" s="13">
+        <v>1</v>
+      </c>
+      <c r="H141" s="13">
         <v>2</v>
       </c>
-      <c r="H141" s="13">
-        <v>1</v>
-      </c>
       <c r="I141" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J141" s="4">
         <v>38</v>
       </c>
       <c r="K141" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L141" s="4" t="s">
         <v>13</v>
@@ -9349,7 +9344,7 @@
     </row>
     <row r="142" spans="1:16">
       <c r="A142" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>305</v>
@@ -9361,25 +9356,25 @@
         <v>1</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F142" s="13">
         <v>1</v>
       </c>
       <c r="G142" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H142" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I142" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J142" s="4">
         <v>38</v>
       </c>
       <c r="K142" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L142" s="4" t="s">
         <v>13</v>
@@ -9397,7 +9392,7 @@
     </row>
     <row r="143" spans="1:16">
       <c r="A143" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>307</v>
@@ -9406,28 +9401,25 @@
         <v>308</v>
       </c>
       <c r="D143" s="13">
-        <v>1</v>
-      </c>
-      <c r="E143" s="13" t="s">
-        <v>399</v>
+        <v>0</v>
       </c>
       <c r="F143" s="13">
         <v>1</v>
       </c>
       <c r="G143" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H143" s="13">
         <v>1</v>
       </c>
       <c r="I143" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J143" s="4">
         <v>38</v>
       </c>
       <c r="K143" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L143" s="4" t="s">
         <v>13</v>
@@ -9445,7 +9437,7 @@
     </row>
     <row r="144" spans="1:16">
       <c r="A144" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>309</v>
@@ -9460,19 +9452,19 @@
         <v>1</v>
       </c>
       <c r="G144" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H144" s="13">
         <v>1</v>
       </c>
       <c r="I144" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J144" s="4">
         <v>38</v>
       </c>
       <c r="K144" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L144" s="4" t="s">
         <v>13</v>
@@ -9490,7 +9482,7 @@
     </row>
     <row r="145" spans="1:16">
       <c r="A145" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>311</v>
@@ -9505,19 +9497,19 @@
         <v>1</v>
       </c>
       <c r="G145" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H145" s="13">
         <v>1</v>
       </c>
       <c r="I145" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J145" s="4">
         <v>38</v>
       </c>
       <c r="K145" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L145" s="4" t="s">
         <v>13</v>
@@ -9535,40 +9527,43 @@
     </row>
     <row r="146" spans="1:16">
       <c r="A146" s="4" t="s">
-        <v>277</v>
+        <v>313</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D146" s="13">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E146" s="13" t="s">
+        <v>399</v>
       </c>
       <c r="F146" s="13">
         <v>1</v>
       </c>
       <c r="G146" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H146" s="13">
         <v>1</v>
       </c>
       <c r="I146" s="4">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="J146" s="4">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K146" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L146" s="4" t="s">
         <v>13</v>
       </c>
       <c r="M146" s="4">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="N146" s="4">
         <v>1</v>
@@ -9580,7 +9575,7 @@
     </row>
     <row r="147" spans="1:16">
       <c r="A147" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>316</v>
@@ -9592,25 +9587,25 @@
         <v>1</v>
       </c>
       <c r="E147" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F147" s="13">
         <v>1</v>
       </c>
       <c r="G147" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H147" s="13">
         <v>1</v>
       </c>
       <c r="I147" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J147" s="4">
         <v>41</v>
       </c>
       <c r="K147" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L147" s="4" t="s">
         <v>13</v>
@@ -9628,7 +9623,7 @@
     </row>
     <row r="148" spans="1:16">
       <c r="A148" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>318</v>
@@ -9640,25 +9635,25 @@
         <v>1</v>
       </c>
       <c r="E148" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F148" s="13">
         <v>1</v>
       </c>
       <c r="G148" s="13">
+        <v>1</v>
+      </c>
+      <c r="H148" s="13">
         <v>2</v>
       </c>
-      <c r="H148" s="13">
-        <v>1</v>
-      </c>
       <c r="I148" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J148" s="4">
         <v>41</v>
       </c>
       <c r="K148" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L148" s="4" t="s">
         <v>13</v>
@@ -9676,7 +9671,7 @@
     </row>
     <row r="149" spans="1:16">
       <c r="A149" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>320</v>
@@ -9688,7 +9683,7 @@
         <v>1</v>
       </c>
       <c r="E149" s="13" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="F149" s="13">
         <v>1</v>
@@ -9700,13 +9695,13 @@
         <v>2</v>
       </c>
       <c r="I149" s="4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J149" s="4">
         <v>41</v>
       </c>
       <c r="K149" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L149" s="4" t="s">
         <v>13</v>
@@ -9724,37 +9719,37 @@
     </row>
     <row r="150" spans="1:16">
       <c r="A150" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="C150" s="14" t="s">
+      <c r="C150" s="9" t="s">
         <v>323</v>
       </c>
       <c r="D150" s="13">
         <v>1</v>
       </c>
       <c r="E150" s="13" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F150" s="13">
         <v>1</v>
       </c>
       <c r="G150" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H150" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I150" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J150" s="4">
         <v>41</v>
       </c>
       <c r="K150" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L150" s="4" t="s">
         <v>13</v>
@@ -9772,37 +9767,37 @@
     </row>
     <row r="151" spans="1:16">
       <c r="A151" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="C151" s="9" t="s">
+      <c r="C151" s="14" t="s">
         <v>325</v>
       </c>
       <c r="D151" s="13">
         <v>1</v>
       </c>
       <c r="E151" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F151" s="13">
         <v>1</v>
       </c>
       <c r="G151" s="13">
+        <v>1</v>
+      </c>
+      <c r="H151" s="13">
         <v>2</v>
       </c>
-      <c r="H151" s="13">
-        <v>1</v>
-      </c>
       <c r="I151" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J151" s="4">
         <v>41</v>
       </c>
       <c r="K151" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L151" s="4" t="s">
         <v>13</v>
@@ -9820,7 +9815,7 @@
     </row>
     <row r="152" spans="1:16">
       <c r="A152" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>326</v>
@@ -9832,25 +9827,25 @@
         <v>1</v>
       </c>
       <c r="E152" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F152" s="13">
         <v>1</v>
       </c>
       <c r="G152" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H152" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I152" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J152" s="4">
         <v>41</v>
       </c>
       <c r="K152" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L152" s="4" t="s">
         <v>13</v>
@@ -9868,37 +9863,37 @@
     </row>
     <row r="153" spans="1:16">
       <c r="A153" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>328</v>
       </c>
       <c r="C153" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D153" s="13">
         <v>1</v>
       </c>
       <c r="E153" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F153" s="13">
         <v>1</v>
       </c>
       <c r="G153" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H153" s="13">
         <v>1</v>
       </c>
       <c r="I153" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J153" s="4">
         <v>41</v>
       </c>
       <c r="K153" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L153" s="4" t="s">
         <v>13</v>
@@ -9916,37 +9911,37 @@
     </row>
     <row r="154" spans="1:16">
       <c r="A154" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D154" s="13">
         <v>1</v>
       </c>
       <c r="E154" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F154" s="13">
         <v>1</v>
       </c>
       <c r="G154" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H154" s="13">
         <v>1</v>
       </c>
       <c r="I154" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J154" s="4">
         <v>41</v>
       </c>
       <c r="K154" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L154" s="4" t="s">
         <v>13</v>
@@ -9964,37 +9959,34 @@
     </row>
     <row r="155" spans="1:16">
       <c r="A155" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C155" s="14" t="s">
         <v>333</v>
       </c>
       <c r="D155" s="13">
-        <v>1</v>
-      </c>
-      <c r="E155" s="13" t="s">
-        <v>399</v>
+        <v>0</v>
       </c>
       <c r="F155" s="13">
         <v>1</v>
       </c>
       <c r="G155" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H155" s="13">
         <v>1</v>
       </c>
       <c r="I155" s="4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J155" s="4">
         <v>41</v>
       </c>
       <c r="K155" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L155" s="4" t="s">
         <v>13</v>
@@ -10012,7 +10004,7 @@
     </row>
     <row r="156" spans="1:16">
       <c r="A156" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>334</v>
@@ -10021,25 +10013,28 @@
         <v>335</v>
       </c>
       <c r="D156" s="13">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E156" s="13" t="s">
+        <v>399</v>
       </c>
       <c r="F156" s="13">
         <v>1</v>
       </c>
       <c r="G156" s="13">
+        <v>1</v>
+      </c>
+      <c r="H156" s="13">
         <v>2</v>
       </c>
-      <c r="H156" s="13">
-        <v>1</v>
-      </c>
       <c r="I156" s="4">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J156" s="4">
         <v>41</v>
       </c>
       <c r="K156" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L156" s="4" t="s">
         <v>13</v>
@@ -10057,37 +10052,37 @@
     </row>
     <row r="157" spans="1:16">
       <c r="A157" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>336</v>
       </c>
       <c r="C157" s="14" t="s">
-        <v>337</v>
+        <v>298</v>
       </c>
       <c r="D157" s="13">
         <v>1</v>
       </c>
       <c r="E157" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F157" s="13">
         <v>1</v>
       </c>
       <c r="G157" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H157" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I157" s="4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J157" s="4">
         <v>41</v>
       </c>
       <c r="K157" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L157" s="4" t="s">
         <v>13</v>
@@ -10105,13 +10100,13 @@
     </row>
     <row r="158" spans="1:16">
       <c r="A158" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C158" s="14" t="s">
-        <v>300</v>
+        <v>339</v>
       </c>
       <c r="D158" s="13">
         <v>1</v>
@@ -10123,19 +10118,19 @@
         <v>1</v>
       </c>
       <c r="G158" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H158" s="13">
         <v>1</v>
       </c>
       <c r="I158" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J158" s="4">
         <v>41</v>
       </c>
       <c r="K158" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L158" s="4" t="s">
         <v>13</v>
@@ -10153,37 +10148,37 @@
     </row>
     <row r="159" spans="1:16">
       <c r="A159" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C159" s="14" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D159" s="13">
         <v>1</v>
       </c>
       <c r="E159" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F159" s="13">
         <v>1</v>
       </c>
       <c r="G159" s="13">
+        <v>1</v>
+      </c>
+      <c r="H159" s="13">
         <v>2</v>
       </c>
-      <c r="H159" s="13">
-        <v>1</v>
-      </c>
       <c r="I159" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J159" s="4">
         <v>41</v>
       </c>
       <c r="K159" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L159" s="4" t="s">
         <v>13</v>
@@ -10201,19 +10196,19 @@
     </row>
     <row r="160" spans="1:16">
       <c r="A160" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>340</v>
+        <v>406</v>
       </c>
       <c r="C160" s="14" t="s">
-        <v>342</v>
+        <v>304</v>
       </c>
       <c r="D160" s="13">
         <v>1</v>
       </c>
       <c r="E160" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F160" s="13">
         <v>1</v>
@@ -10225,13 +10220,13 @@
         <v>2</v>
       </c>
       <c r="I160" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J160" s="4">
         <v>41</v>
       </c>
       <c r="K160" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L160" s="4" t="s">
         <v>13</v>
@@ -10249,10 +10244,10 @@
     </row>
     <row r="161" spans="1:16">
       <c r="A161" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>408</v>
+        <v>341</v>
       </c>
       <c r="C161" s="14" t="s">
         <v>306</v>
@@ -10261,25 +10256,25 @@
         <v>1</v>
       </c>
       <c r="E161" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F161" s="13">
         <v>1</v>
       </c>
       <c r="G161" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H161" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I161" s="4">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J161" s="4">
         <v>41</v>
       </c>
       <c r="K161" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L161" s="4" t="s">
         <v>13</v>
@@ -10297,37 +10292,34 @@
     </row>
     <row r="162" spans="1:16">
       <c r="A162" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C162" s="14" t="s">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="D162" s="13">
-        <v>1</v>
-      </c>
-      <c r="E162" s="13" t="s">
-        <v>399</v>
+        <v>0</v>
       </c>
       <c r="F162" s="13">
         <v>1</v>
       </c>
       <c r="G162" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H162" s="13">
         <v>1</v>
       </c>
       <c r="I162" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J162" s="4">
         <v>41</v>
       </c>
       <c r="K162" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L162" s="4" t="s">
         <v>13</v>
@@ -10345,13 +10337,13 @@
     </row>
     <row r="163" spans="1:16">
       <c r="A163" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C163" s="14" t="s">
-        <v>346</v>
+        <v>310</v>
       </c>
       <c r="D163" s="13">
         <v>0</v>
@@ -10360,19 +10352,19 @@
         <v>1</v>
       </c>
       <c r="G163" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H163" s="13">
         <v>1</v>
       </c>
       <c r="I163" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J163" s="4">
         <v>41</v>
       </c>
       <c r="K163" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L163" s="4" t="s">
         <v>13</v>
@@ -10390,13 +10382,13 @@
     </row>
     <row r="164" spans="1:16">
       <c r="A164" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>345</v>
       </c>
       <c r="C164" s="14" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="D164" s="13">
         <v>0</v>
@@ -10405,19 +10397,19 @@
         <v>1</v>
       </c>
       <c r="G164" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H164" s="13">
         <v>1</v>
       </c>
       <c r="I164" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J164" s="4">
         <v>41</v>
       </c>
       <c r="K164" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L164" s="4" t="s">
         <v>13</v>
@@ -10435,14 +10427,14 @@
     </row>
     <row r="165" spans="1:16">
       <c r="A165" s="4" t="s">
-        <v>315</v>
+        <v>347</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="C165" s="14" t="s">
         <v>348</v>
       </c>
+      <c r="C165" s="9" t="s">
+        <v>349</v>
+      </c>
       <c r="D165" s="13">
         <v>0</v>
       </c>
@@ -10450,25 +10442,25 @@
         <v>1</v>
       </c>
       <c r="G165" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H165" s="13">
         <v>1</v>
       </c>
       <c r="I165" s="4">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="J165" s="4">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K165" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L165" s="4" t="s">
         <v>13</v>
       </c>
       <c r="M165" s="4">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="N165" s="4">
         <v>1</v>
@@ -10480,12 +10472,12 @@
     </row>
     <row r="166" spans="1:16">
       <c r="A166" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="C166" s="9" t="s">
+      <c r="C166" s="14" t="s">
         <v>351</v>
       </c>
       <c r="D166" s="13">
@@ -10495,19 +10487,19 @@
         <v>1</v>
       </c>
       <c r="G166" s="13">
+        <v>0</v>
+      </c>
+      <c r="H166" s="13">
+        <v>1</v>
+      </c>
+      <c r="I166" s="4">
         <v>2</v>
-      </c>
-      <c r="H166" s="13">
-        <v>1</v>
-      </c>
-      <c r="I166" s="4">
-        <v>1</v>
       </c>
       <c r="J166" s="4">
         <v>46</v>
       </c>
       <c r="K166" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L166" s="4" t="s">
         <v>13</v>
@@ -10525,7 +10517,7 @@
     </row>
     <row r="167" spans="1:16">
       <c r="A167" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>352</v>
@@ -10540,19 +10532,19 @@
         <v>1</v>
       </c>
       <c r="G167" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H167" s="13">
         <v>1</v>
       </c>
       <c r="I167" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J167" s="4">
         <v>46</v>
       </c>
       <c r="K167" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L167" s="4" t="s">
         <v>13</v>
@@ -10570,7 +10562,7 @@
     </row>
     <row r="168" spans="1:16">
       <c r="A168" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>354</v>
@@ -10579,25 +10571,28 @@
         <v>355</v>
       </c>
       <c r="D168" s="13">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E168" s="13" t="s">
+        <v>399</v>
       </c>
       <c r="F168" s="13">
         <v>1</v>
       </c>
       <c r="G168" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H168" s="13">
         <v>1</v>
       </c>
       <c r="I168" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J168" s="4">
         <v>46</v>
       </c>
       <c r="K168" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L168" s="4" t="s">
         <v>13</v>
@@ -10615,7 +10610,7 @@
     </row>
     <row r="169" spans="1:16">
       <c r="A169" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B169" s="4" t="s">
         <v>356</v>
@@ -10627,25 +10622,25 @@
         <v>1</v>
       </c>
       <c r="E169" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F169" s="13">
         <v>1</v>
       </c>
       <c r="G169" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H169" s="13">
         <v>1</v>
       </c>
       <c r="I169" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J169" s="4">
         <v>46</v>
       </c>
       <c r="K169" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L169" s="4" t="s">
         <v>13</v>
@@ -10663,7 +10658,7 @@
     </row>
     <row r="170" spans="1:16">
       <c r="A170" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>358</v>
@@ -10681,19 +10676,19 @@
         <v>1</v>
       </c>
       <c r="G170" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H170" s="13">
         <v>1</v>
       </c>
       <c r="I170" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J170" s="4">
         <v>46</v>
       </c>
       <c r="K170" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L170" s="4" t="s">
         <v>13</v>
@@ -10711,7 +10706,7 @@
     </row>
     <row r="171" spans="1:16">
       <c r="A171" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>360</v>
@@ -10723,25 +10718,25 @@
         <v>1</v>
       </c>
       <c r="E171" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F171" s="13">
         <v>1</v>
       </c>
       <c r="G171" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H171" s="13">
         <v>1</v>
       </c>
       <c r="I171" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J171" s="4">
         <v>46</v>
       </c>
       <c r="K171" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L171" s="4" t="s">
         <v>13</v>
@@ -10759,37 +10754,37 @@
     </row>
     <row r="172" spans="1:16">
       <c r="A172" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="C172" s="14" t="s">
+      <c r="C172" s="9" t="s">
         <v>363</v>
       </c>
       <c r="D172" s="13">
         <v>1</v>
       </c>
       <c r="E172" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F172" s="13">
         <v>1</v>
       </c>
       <c r="G172" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H172" s="13">
         <v>1</v>
       </c>
       <c r="I172" s="4">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J172" s="4">
         <v>46</v>
       </c>
       <c r="K172" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L172" s="4" t="s">
         <v>13</v>
@@ -10807,7 +10802,7 @@
     </row>
     <row r="173" spans="1:16">
       <c r="A173" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>364</v>
@@ -10819,25 +10814,25 @@
         <v>1</v>
       </c>
       <c r="E173" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F173" s="13">
         <v>1</v>
       </c>
       <c r="G173" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H173" s="13">
         <v>1</v>
       </c>
       <c r="I173" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J173" s="4">
         <v>46</v>
       </c>
       <c r="K173" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L173" s="4" t="s">
         <v>13</v>
@@ -10855,7 +10850,7 @@
     </row>
     <row r="174" spans="1:16">
       <c r="A174" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>366</v>
@@ -10873,19 +10868,19 @@
         <v>1</v>
       </c>
       <c r="G174" s="13">
+        <v>1</v>
+      </c>
+      <c r="H174" s="13">
         <v>2</v>
       </c>
-      <c r="H174" s="13">
-        <v>1</v>
-      </c>
       <c r="I174" s="4">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J174" s="4">
         <v>46</v>
       </c>
       <c r="K174" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L174" s="4" t="s">
         <v>13</v>
@@ -10903,7 +10898,7 @@
     </row>
     <row r="175" spans="1:16">
       <c r="A175" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>368</v>
@@ -10915,25 +10910,25 @@
         <v>1</v>
       </c>
       <c r="E175" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F175" s="13">
         <v>1</v>
       </c>
       <c r="G175" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H175" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I175" s="4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J175" s="4">
         <v>46</v>
       </c>
       <c r="K175" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L175" s="4" t="s">
         <v>13</v>
@@ -10951,7 +10946,7 @@
     </row>
     <row r="176" spans="1:16">
       <c r="A176" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>370</v>
@@ -10963,25 +10958,25 @@
         <v>1</v>
       </c>
       <c r="E176" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F176" s="13">
         <v>1</v>
       </c>
       <c r="G176" s="13">
+        <v>1</v>
+      </c>
+      <c r="H176" s="13">
         <v>2</v>
       </c>
-      <c r="H176" s="13">
-        <v>1</v>
-      </c>
       <c r="I176" s="4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J176" s="4">
         <v>46</v>
       </c>
       <c r="K176" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L176" s="4" t="s">
         <v>13</v>
@@ -10999,7 +10994,7 @@
     </row>
     <row r="177" spans="1:16">
       <c r="A177" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>372</v>
@@ -11011,25 +11006,25 @@
         <v>1</v>
       </c>
       <c r="E177" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F177" s="13">
         <v>1</v>
       </c>
       <c r="G177" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H177" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I177" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J177" s="4">
         <v>46</v>
       </c>
       <c r="K177" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L177" s="4" t="s">
         <v>13</v>
@@ -11047,7 +11042,7 @@
     </row>
     <row r="178" spans="1:16">
       <c r="A178" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>374</v>
@@ -11059,25 +11054,25 @@
         <v>1</v>
       </c>
       <c r="E178" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F178" s="13">
         <v>1</v>
       </c>
       <c r="G178" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H178" s="13">
         <v>1</v>
       </c>
       <c r="I178" s="4">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J178" s="4">
         <v>46</v>
       </c>
       <c r="K178" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L178" s="4" t="s">
         <v>13</v>
@@ -11095,7 +11090,7 @@
     </row>
     <row r="179" spans="1:16">
       <c r="A179" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>376</v>
@@ -11113,19 +11108,19 @@
         <v>1</v>
       </c>
       <c r="G179" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H179" s="13">
         <v>1</v>
       </c>
       <c r="I179" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J179" s="4">
         <v>46</v>
       </c>
       <c r="K179" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L179" s="4" t="s">
         <v>13</v>
@@ -11143,7 +11138,7 @@
     </row>
     <row r="180" spans="1:16">
       <c r="A180" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>378</v>
@@ -11155,25 +11150,25 @@
         <v>1</v>
       </c>
       <c r="E180" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F180" s="13">
         <v>1</v>
       </c>
       <c r="G180" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H180" s="13">
         <v>1</v>
       </c>
       <c r="I180" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J180" s="4">
         <v>46</v>
       </c>
       <c r="K180" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L180" s="4" t="s">
         <v>13</v>
@@ -11191,7 +11186,7 @@
     </row>
     <row r="181" spans="1:16">
       <c r="A181" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>380</v>
@@ -11203,25 +11198,25 @@
         <v>1</v>
       </c>
       <c r="E181" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F181" s="13">
         <v>1</v>
       </c>
       <c r="G181" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H181" s="13">
         <v>1</v>
       </c>
       <c r="I181" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J181" s="4">
         <v>46</v>
       </c>
       <c r="K181" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L181" s="4" t="s">
         <v>13</v>
@@ -11237,39 +11232,39 @@
       </c>
       <c r="P181" s="4"/>
     </row>
-    <row r="182" spans="1:16">
+    <row r="182" spans="1:16" ht="46" customHeight="1">
       <c r="A182" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B182" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C182" s="9" t="s">
         <v>382</v>
       </c>
-      <c r="C182" s="9" t="s">
-        <v>383</v>
-      </c>
       <c r="D182" s="13">
         <v>1</v>
       </c>
       <c r="E182" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F182" s="13">
         <v>1</v>
       </c>
       <c r="G182" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H182" s="13">
         <v>1</v>
       </c>
       <c r="I182" s="4">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J182" s="4">
         <v>46</v>
       </c>
       <c r="K182" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L182" s="4" t="s">
         <v>13</v>
@@ -11285,39 +11280,36 @@
       </c>
       <c r="P182" s="4"/>
     </row>
-    <row r="183" spans="1:16" ht="46" customHeight="1">
+    <row r="183" spans="1:16">
       <c r="A183" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C183" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D183" s="13">
-        <v>1</v>
-      </c>
-      <c r="E183" s="13" t="s">
-        <v>399</v>
+        <v>0</v>
       </c>
       <c r="F183" s="13">
         <v>1</v>
       </c>
       <c r="G183" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H183" s="13">
         <v>1</v>
       </c>
       <c r="I183" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J183" s="4">
         <v>46</v>
       </c>
       <c r="K183" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L183" s="4" t="s">
         <v>13</v>
@@ -11335,13 +11327,13 @@
     </row>
     <row r="184" spans="1:16">
       <c r="A184" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C184" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D184" s="13">
         <v>0</v>
@@ -11350,19 +11342,19 @@
         <v>1</v>
       </c>
       <c r="G184" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H184" s="13">
         <v>1</v>
       </c>
       <c r="I184" s="4">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J184" s="4">
         <v>46</v>
       </c>
       <c r="K184" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L184" s="4" t="s">
         <v>13</v>
@@ -11380,10 +11372,10 @@
     </row>
     <row r="185" spans="1:16">
       <c r="A185" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C185" s="9" t="s">
         <v>386</v>
@@ -11395,19 +11387,19 @@
         <v>1</v>
       </c>
       <c r="G185" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H185" s="13">
         <v>1</v>
       </c>
       <c r="I185" s="4">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J185" s="4">
         <v>46</v>
       </c>
       <c r="K185" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L185" s="4" t="s">
         <v>13</v>
@@ -11422,51 +11414,6 @@
         <v>1</v>
       </c>
       <c r="P185" s="4"/>
-    </row>
-    <row r="186" spans="1:16">
-      <c r="A186" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="B186" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="C186" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="D186" s="13">
-        <v>0</v>
-      </c>
-      <c r="F186" s="13">
-        <v>1</v>
-      </c>
-      <c r="G186" s="13">
-        <v>2</v>
-      </c>
-      <c r="H186" s="13">
-        <v>1</v>
-      </c>
-      <c r="I186" s="4">
-        <v>46</v>
-      </c>
-      <c r="J186" s="4">
-        <v>46</v>
-      </c>
-      <c r="K186" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="L186" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="M186" s="4">
-        <v>2025</v>
-      </c>
-      <c r="N186" s="4">
-        <v>1</v>
-      </c>
-      <c r="O186" s="4">
-        <v>1</v>
-      </c>
-      <c r="P186" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -11485,26 +11432,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="15" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -11523,21 +11470,21 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="15" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -11551,16 +11498,16 @@
       </c>
       <c r="C8">
         <f>COUNTIF(Sheet1!D:D,"1")</f>
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D8">
         <f>SUM(A8:C8)</f>
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="17" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -11578,23 +11525,23 @@
       </c>
       <c r="C12">
         <f>COUNTIF(Sheet1!D:D,"1")</f>
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="C14" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="C15" s="16">
         <f>COUNTIF(Sheet1!E:E,"Low")</f>
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="C16" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -11605,7 +11552,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="C18" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -11616,7 +11563,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="18" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C21" s="19"/>
     </row>
@@ -11625,11 +11572,11 @@
         <v>0</v>
       </c>
       <c r="C22" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F22">
         <f>COUNTIF(Sheet1!H:H,"0")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -11637,7 +11584,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F23">
         <f>COUNTIF(Sheet1!H:H,"1")</f>
@@ -11649,7 +11596,7 @@
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F24">
         <f>COUNTIF(Sheet1!H:H,"2")</f>
